--- a/jogos_2024-08-29.xlsx
+++ b/jogos_2024-08-29.xlsx
@@ -901,16 +901,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Urooba</t>
+          <t>Dibba Al Hisn</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>5.35</v>
+        <v>5.8</v>
       </c>
       <c r="N4" t="n">
-        <v>6.4</v>
+        <v>7.44</v>
       </c>
       <c r="O4" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P4" t="n">
         <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
         <v>1.2</v>
@@ -951,41 +951,41 @@
         <v>4.33</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="U4" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['45', '90+6']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.38</v>
+        <v>3.78</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45533.45486111111</v>
@@ -1030,16 +1030,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dibba Al Hisn</t>
+          <t>Al Urooba</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
-        <v>5.8</v>
+        <v>5.35</v>
       </c>
       <c r="N5" t="n">
-        <v>7.44</v>
+        <v>6.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="P5" t="n">
         <v>2.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R5" t="n">
         <v>1.2</v>
@@ -1080,41 +1080,41 @@
         <v>4.33</v>
       </c>
       <c r="T5" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['45', '90+6']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.78</v>
+        <v>3.38</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45533.45486111111</v>
@@ -1159,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Havadar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1185,31 +1185,31 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.45</v>
+        <v>5.25</v>
       </c>
       <c r="M6" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>1.62</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="T6" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="U6" t="n">
         <v>1.25</v>
@@ -1218,16 +1218,16 @@
         <v>1.06</v>
       </c>
       <c r="W6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z6" t="n">
         <v>1.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.3</v>
       </c>
       <c r="AA6" t="n">
         <v>4.75</v>
@@ -1236,32 +1236,32 @@
         <v>1.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['15', '64', '90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['30', '59', '75', '85']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45533.53125</v>
@@ -1288,57 +1288,57 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Havadar</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="O7" t="n">
-        <v>6</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S7" t="n">
         <v>2.3</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.35</v>
-      </c>
       <c r="T7" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="U7" t="n">
         <v>1.25</v>
@@ -1347,16 +1347,16 @@
         <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AA7" t="n">
         <v>4.75</v>
@@ -1365,32 +1365,32 @@
         <v>1.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '64', '90+5']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['30', '59', '75', '85']</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.9</v>
+        <v>1.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45533.53125</v>
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M9" t="n">
         <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R9" t="n">
         <v>1.44</v>
@@ -1602,53 +1602,53 @@
         <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="X9" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['16', '58']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['48', '73']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['86']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['73']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AI9" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45533.54166666666</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
         <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.25</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
         <v>1.3</v>
       </c>
-      <c r="X10" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['11', '52', '77']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['33']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45533.54166666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
         <v>1.05</v>
       </c>
       <c r="W11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.33</v>
       </c>
-      <c r="X11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['42']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA11" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['16', '58']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['48', '73']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>1.25</v>
       </c>
-      <c r="AH11" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AI11" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45533.54166666666</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.91</v>
+        <v>5.25</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.44</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="X12" t="n">
-        <v>3.34</v>
+        <v>2.98</v>
       </c>
       <c r="Y12" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Z12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA12" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['26', '45+1']</t>
+          <t>['47', '51', '78']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.84</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.95</v>
+        <v>1.18</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45533.54166666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="M13" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="P13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z13" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AA13" t="n">
-        <v>4.5</v>
+        <v>3.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['26', '45+1']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45533.54166666666</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,22 +2217,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.25</v>
+        <v>2.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
@@ -2247,25 +2247,25 @@
         <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X14" t="n">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.98</v>
+        <v>3.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
         <v>1.8</v>
@@ -2275,25 +2275,25 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['11', '52', '77']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['47', '51', '78']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45533.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2604,65 +2604,65 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>4.78</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.93</v>
+        <v>1.67</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="P17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>2.34</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="X17" t="n">
-        <v>4.33</v>
+        <v>2.48</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['34', '53', '56', '90']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.4</v>
+        <v>1.14</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45533.58333333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,65 +2733,65 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q18" t="n">
         <v>5</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O18" t="n">
-        <v>6</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['34', '53', '56', '90']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.14</v>
+        <v>2.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.75</v>
+        <v>1.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45533.58333333334</v>
@@ -2836,16 +2836,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.83</v>
+        <v>1.79</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>3.99</v>
       </c>
       <c r="N19" t="n">
-        <v>1.87</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.42</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.81</v>
+        <v>2.38</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>3.28</v>
+        <v>4.45</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.88</v>
+        <v>1.59</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.82</v>
+        <v>2.37</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.18</v>
+        <v>2.24</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['70', '90+8']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.23</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.51</v>
+        <v>1.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.64</v>
+        <v>2.6</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45533.625</v>
@@ -2965,16 +2965,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>3.83</v>
       </c>
       <c r="M20" t="n">
-        <v>3.99</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>3.85</v>
+        <v>1.87</v>
       </c>
       <c r="O20" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="X20" t="n">
-        <v>4.45</v>
+        <v>3.28</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.37</v>
+        <v>1.82</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.24</v>
+        <v>3.18</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['70', '90+8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.95</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.5</v>
+        <v>2.51</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45533.625</v>

--- a/jogos_2024-08-29.xlsx
+++ b/jogos_2024-08-29.xlsx
@@ -901,16 +901,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dibba Al Hisn</t>
+          <t>Al Urooba</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8</v>
+        <v>5.35</v>
       </c>
       <c r="N4" t="n">
-        <v>7.44</v>
+        <v>6.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="P4" t="n">
         <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.2</v>
@@ -951,41 +951,41 @@
         <v>4.33</v>
       </c>
       <c r="T4" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['45', '90+6']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.78</v>
+        <v>3.38</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45533.45486111111</v>
@@ -1030,16 +1030,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Urooba</t>
+          <t>Dibba Al Hisn</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>5.35</v>
+        <v>5.8</v>
       </c>
       <c r="N5" t="n">
-        <v>6.4</v>
+        <v>7.44</v>
       </c>
       <c r="O5" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P5" t="n">
         <v>2.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
         <v>1.2</v>
@@ -1080,41 +1080,41 @@
         <v>4.33</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="U5" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['45', '90+6']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.38</v>
+        <v>3.78</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45533.45486111111</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="M9" t="n">
         <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
         <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD9" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['16', '58']</t>
+          <t>['11', '52', '77']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['48', '73']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG9" t="n">
         <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45533.54166666666</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
         <v>3.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y10" t="n">
         <v>3.25</v>
       </c>
-      <c r="U10" t="n">
+      <c r="Z10" t="n">
         <v>1.33</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AA10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45533.54166666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="T11" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
         <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="X11" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.5</v>
+        <v>3.64</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>['16', '58']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['48', '73']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45533.54166666666</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M14" t="n">
         <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T14" t="n">
         <v>3.25</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
         <v>1.3</v>
       </c>
-      <c r="X14" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['11', '52', '77']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['33']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45533.54166666666</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="M15" t="n">
-        <v>4.25</v>
+        <v>3.88</v>
       </c>
       <c r="N15" t="n">
-        <v>4.38</v>
+        <v>3.73</v>
       </c>
       <c r="O15" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.72</v>
+        <v>3.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>5.5</v>
+        <v>4.81</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AD15" t="n">
         <v>2.4</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['14', '53', '65', '75']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45533.5625</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="M16" t="n">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.73</v>
+        <v>4.38</v>
       </c>
       <c r="O16" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="P16" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.9</v>
+        <v>4.72</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>4.81</v>
+        <v>5.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AD16" t="n">
         <v>2.4</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['14', '53', '65', '75']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45533.5625</v>
